--- a/5_simulation/outputs/tables/supplementary/S3_quintile_results.xlsx
+++ b/5_simulation/outputs/tables/supplementary/S3_quintile_results.xlsx
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35.4328016749</v>
+        <v>35.4576103421</v>
       </c>
       <c r="D2" t="n">
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>102.970246461</v>
+        <v>103.136729273</v>
       </c>
       <c r="F2" t="n">
-        <v>3.55063484487</v>
+        <v>3.5156441499</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -494,7 +494,7 @@
         <v>50.0036556913</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05468278413</v>
+        <v>3.11246482853</v>
       </c>
     </row>
     <row r="3">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.646270697393</v>
+        <v>0.652907195144</v>
       </c>
       <c r="D3" t="n">
-        <v>17.8084994432</v>
+        <v>17.9167692716</v>
       </c>
       <c r="E3" t="n">
-        <v>102.852689434</v>
+        <v>103.020846365</v>
       </c>
       <c r="F3" t="n">
-        <v>1.48442375597</v>
+        <v>1.45295538619</v>
       </c>
       <c r="G3" t="n">
         <v>100</v>
@@ -527,7 +527,7 @@
         <v>49.9963443087</v>
       </c>
       <c r="I3" t="n">
-        <v>7.732594344</v>
+        <v>8.301932964180001</v>
       </c>
     </row>
     <row r="4">
@@ -548,10 +548,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>102.75544715</v>
+        <v>102.922323306</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.76784054683</v>
+        <v>-1.79509987688</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>99.68785022039999</v>
+        <v>99.62334827949999</v>
       </c>
     </row>
     <row r="5">
@@ -581,10 +581,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>102.672178414</v>
+        <v>102.838874194</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.69350858346</v>
+        <v>-1.72225020131</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>99.73630971919999</v>
+        <v>99.6106801749</v>
       </c>
     </row>
     <row r="6">
@@ -614,10 +614,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>102.520157837</v>
+        <v>102.682590086</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.53935089076</v>
+        <v>-1.56202224146</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>97.1121736275</v>
+        <v>95.94421302809999</v>
       </c>
     </row>
     <row r="7">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.8711521945</v>
+        <v>35.8958451481</v>
       </c>
       <c r="D7" t="n">
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>102.958119124</v>
+        <v>103.124021045</v>
       </c>
       <c r="F7" t="n">
-        <v>2.78345455865</v>
+        <v>2.74868383993</v>
       </c>
       <c r="G7" t="n">
         <v>86.24235989349999</v>
@@ -659,7 +659,7 @@
         <v>43.1243327012</v>
       </c>
       <c r="I7" t="n">
-        <v>15.5176677944</v>
+        <v>15.5484850393</v>
       </c>
     </row>
     <row r="8">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.823053699994</v>
+        <v>0.830365001051</v>
       </c>
       <c r="D8" t="n">
-        <v>20.2823423741</v>
+        <v>20.4512244556</v>
       </c>
       <c r="E8" t="n">
-        <v>102.840642442</v>
+        <v>103.008223249</v>
       </c>
       <c r="F8" t="n">
-        <v>0.100076607568</v>
+        <v>0.0693343682723</v>
       </c>
       <c r="G8" t="n">
         <v>58.8145575322</v>
@@ -692,7 +692,7 @@
         <v>29.4051286874</v>
       </c>
       <c r="I8" t="n">
-        <v>44.377823709</v>
+        <v>44.5784234179</v>
       </c>
     </row>
     <row r="9">
@@ -713,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>102.743539559</v>
+        <v>102.909846101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.922461337227</v>
+        <v>-0.950202246614</v>
       </c>
       <c r="G9" t="n">
         <v>34.3003394119</v>
@@ -725,7 +725,7 @@
         <v>17.1644274396</v>
       </c>
       <c r="I9" t="n">
-        <v>70.8500681859</v>
+        <v>70.9968774721</v>
       </c>
     </row>
     <row r="10">
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>102.660358235</v>
+        <v>102.826489409</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.42002906303</v>
+        <v>-1.44889178867</v>
       </c>
       <c r="G10" t="n">
         <v>16.017141461</v>
@@ -758,7 +758,7 @@
         <v>8.01179765713</v>
       </c>
       <c r="I10" t="n">
-        <v>88.71404896350001</v>
+        <v>89.0053785531</v>
       </c>
     </row>
     <row r="11">
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>102.508703506</v>
+        <v>102.670588448</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.49522045685</v>
+        <v>-1.51789199827</v>
       </c>
       <c r="G11" t="n">
         <v>4.58871297208</v>
@@ -791,7 +791,7 @@
         <v>2.2943135146</v>
       </c>
       <c r="I11" t="n">
-        <v>94.13805248760001</v>
+        <v>93.345257825</v>
       </c>
     </row>
     <row r="12">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37.5758441794</v>
+        <v>37.5995811651</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>102.928776138</v>
+        <v>103.093226532</v>
       </c>
       <c r="F12" t="n">
-        <v>0.213404615059</v>
+        <v>0.180040239244</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -824,7 +824,7 @@
         <v>19.996600897</v>
       </c>
       <c r="I12" t="n">
-        <v>28.9957796625</v>
+        <v>29.7378381958</v>
       </c>
     </row>
     <row r="13">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.05703996944</v>
+        <v>1.06543360448</v>
       </c>
       <c r="D13" t="n">
-        <v>22.2308359238</v>
+        <v>22.291404847</v>
       </c>
       <c r="E13" t="n">
-        <v>102.811493715</v>
+        <v>102.977634864</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.529969865456</v>
+        <v>-0.560378965342</v>
       </c>
       <c r="G13" t="n">
         <v>100</v>
@@ -857,7 +857,7 @@
         <v>19.9936770548</v>
       </c>
       <c r="I13" t="n">
-        <v>65.4305610861</v>
+        <v>66.6053963766</v>
       </c>
     </row>
     <row r="14">
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>102.714727637</v>
+        <v>102.879610791</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.780073992387</v>
+        <v>-0.807941980067</v>
       </c>
       <c r="G14" t="n">
         <v>100</v>
@@ -890,7 +890,7 @@
         <v>20.0117618649</v>
       </c>
       <c r="I14" t="n">
-        <v>82.8044498555</v>
+        <v>82.32104276859999</v>
       </c>
     </row>
     <row r="15">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>102.631758063</v>
+        <v>102.796478319</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0098347596</v>
+        <v>-1.0389420777</v>
       </c>
       <c r="G15" t="n">
         <v>100</v>
@@ -923,7 +923,7 @@
         <v>20.0031957001</v>
       </c>
       <c r="I15" t="n">
-        <v>90.2672328438</v>
+        <v>89.28957245460001</v>
       </c>
     </row>
     <row r="16">
@@ -944,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>102.480987841</v>
+        <v>102.6415051</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.15695439133</v>
+        <v>-1.17981068178</v>
       </c>
       <c r="G16" t="n">
         <v>100</v>
@@ -956,7 +956,7 @@
         <v>19.9947644832</v>
       </c>
       <c r="I16" t="n">
-        <v>91.38941395320001</v>
+        <v>90.2936089241</v>
       </c>
     </row>
     <row r="17">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38.0772833025</v>
+        <v>38.0850022221</v>
       </c>
       <c r="D17" t="n">
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>101.590667757</v>
+        <v>101.571419318</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.647032173375</v>
+        <v>-0.659457037297</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>84.813963689</v>
+        <v>85.61523937299999</v>
       </c>
     </row>
     <row r="18">
@@ -1004,16 +1004,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.09861859292</v>
+        <v>1.10129475709</v>
       </c>
       <c r="D18" t="n">
         <v>22.4038035964</v>
       </c>
       <c r="E18" t="n">
-        <v>101.775451036</v>
+        <v>101.756318055</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.73691056636</v>
+        <v>-0.750134375609</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>85.2358659738</v>
+        <v>85.9829299849</v>
       </c>
     </row>
     <row r="19">
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>101.8421875</v>
+        <v>101.822482972</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.793767666339</v>
+        <v>-0.8063912871759999</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>84.06956695380001</v>
+        <v>84.8962540319</v>
       </c>
     </row>
     <row r="20">
@@ -1076,10 +1076,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>101.936432054</v>
+        <v>101.9164501</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.89801824618</v>
+        <v>-0.909903096463</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>86.1596394182</v>
+        <v>86.80212755309999</v>
       </c>
     </row>
     <row r="21">
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>102.00303886</v>
+        <v>101.982923271</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.986029034174</v>
+        <v>-0.997299542363</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>84.84581870549999</v>
+        <v>85.42954449050001</v>
       </c>
     </row>
   </sheetData>
